--- a/data_generation/10_aquatic_toxicity/fenoxaprop-P-ethyl_aquatic_toxicity.xlsx
+++ b/data_generation/10_aquatic_toxicity/fenoxaprop-P-ethyl_aquatic_toxicity.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Data-Work\41_AssessmentPPP-RE\412.34_Projekte\054_derappp\05_Daten\Input\10_aquatic_toxicity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E478779E-3F4C-4644-B66B-45BC2514C1F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6345E9FE-BC76-4426-88E9-250E43B8A6D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3030" yWindow="3030" windowWidth="21600" windowHeight="12525" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aquatic toxicity" sheetId="1" r:id="rId1"/>
@@ -603,31 +603,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V40"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" customWidth="1"/>
-    <col min="3" max="3" width="24.7265625" customWidth="1"/>
-    <col min="4" max="4" width="7.7265625" customWidth="1"/>
-    <col min="5" max="6" width="11.7265625" customWidth="1"/>
-    <col min="7" max="7" width="8.7265625" customWidth="1"/>
-    <col min="8" max="8" width="10.7265625" customWidth="1"/>
-    <col min="9" max="9" width="25.7265625" customWidth="1"/>
-    <col min="10" max="10" width="14.7265625" customWidth="1"/>
-    <col min="11" max="11" width="5.7265625" customWidth="1"/>
-    <col min="12" max="12" width="4.7265625" customWidth="1"/>
-    <col min="13" max="13" width="7.7265625" customWidth="1"/>
-    <col min="14" max="14" width="4.7265625" customWidth="1"/>
-    <col min="15" max="15" width="8.7265625" customWidth="1"/>
-    <col min="16" max="16" width="16.7265625" customWidth="1"/>
-    <col min="17" max="17" width="4.7265625" customWidth="1"/>
-    <col min="18" max="18" width="8.7265625" customWidth="1"/>
-    <col min="19" max="19" width="9.7265625" customWidth="1"/>
-    <col min="20" max="20" width="22.7265625" customWidth="1"/>
-    <col min="21" max="21" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="18.7109375" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
+    <col min="5" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="5.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="7.7109375" customWidth="1"/>
+    <col min="14" max="14" width="4.7109375" customWidth="1"/>
+    <col min="15" max="15" width="8.7109375" customWidth="1"/>
+    <col min="16" max="16" width="16.7109375" customWidth="1"/>
+    <col min="17" max="17" width="4.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="20" max="20" width="22.7109375" customWidth="1"/>
+    <col min="21" max="21" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -695,7 +695,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -748,7 +748,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -801,7 +801,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -854,7 +854,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -907,7 +907,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -966,7 +966,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>21</v>
       </c>
@@ -1025,7 +1025,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -1231,7 +1231,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
@@ -1505,7 +1505,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -1555,7 +1555,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -1605,7 +1605,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -1870,7 +1870,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>21</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -1954,6 +1954,9 @@
       <c r="P25" t="s">
         <v>76</v>
       </c>
+      <c r="Q25">
+        <v>113</v>
+      </c>
       <c r="R25" t="b">
         <v>0</v>
       </c>
@@ -1970,7 +1973,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2001,6 +2004,9 @@
       <c r="P26" t="s">
         <v>76</v>
       </c>
+      <c r="Q26">
+        <v>113</v>
+      </c>
       <c r="R26" t="b">
         <v>0</v>
       </c>
@@ -2017,7 +2023,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2048,6 +2054,9 @@
       <c r="P27" t="s">
         <v>76</v>
       </c>
+      <c r="Q27">
+        <v>113</v>
+      </c>
       <c r="R27" t="b">
         <v>0</v>
       </c>
@@ -2064,7 +2073,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2095,6 +2104,9 @@
       <c r="P28" t="s">
         <v>76</v>
       </c>
+      <c r="Q28">
+        <v>113</v>
+      </c>
       <c r="R28" t="b">
         <v>0</v>
       </c>
@@ -2111,7 +2123,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2142,6 +2154,9 @@
       <c r="P29" t="s">
         <v>76</v>
       </c>
+      <c r="Q29">
+        <v>113</v>
+      </c>
       <c r="R29" t="b">
         <v>0</v>
       </c>
@@ -2158,7 +2173,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -2211,7 +2226,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -2264,7 +2279,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -2317,7 +2332,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -2348,6 +2363,9 @@
       <c r="P33" t="s">
         <v>76</v>
       </c>
+      <c r="Q33">
+        <v>114</v>
+      </c>
       <c r="R33" t="b">
         <v>0</v>
       </c>
@@ -2364,7 +2382,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>21</v>
       </c>
@@ -2395,6 +2413,9 @@
       <c r="P34" t="s">
         <v>76</v>
       </c>
+      <c r="Q34">
+        <v>114</v>
+      </c>
       <c r="R34" t="b">
         <v>0</v>
       </c>
@@ -2411,7 +2432,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>21</v>
       </c>
@@ -2442,6 +2463,9 @@
       <c r="P35" t="s">
         <v>76</v>
       </c>
+      <c r="Q35">
+        <v>114</v>
+      </c>
       <c r="R35" t="b">
         <v>0</v>
       </c>
@@ -2458,7 +2482,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
@@ -2489,6 +2513,9 @@
       <c r="P36" t="s">
         <v>76</v>
       </c>
+      <c r="Q36">
+        <v>114</v>
+      </c>
       <c r="R36" t="b">
         <v>0</v>
       </c>
@@ -2505,7 +2532,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>21</v>
       </c>
@@ -2536,6 +2563,9 @@
       <c r="P37" t="s">
         <v>76</v>
       </c>
+      <c r="Q37">
+        <v>115</v>
+      </c>
       <c r="R37" t="b">
         <v>0</v>
       </c>
@@ -2552,7 +2582,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -2583,6 +2613,9 @@
       <c r="P38" t="s">
         <v>76</v>
       </c>
+      <c r="Q38">
+        <v>115</v>
+      </c>
       <c r="R38" t="b">
         <v>0</v>
       </c>
@@ -2599,7 +2632,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -2630,6 +2663,9 @@
       <c r="P39" t="s">
         <v>76</v>
       </c>
+      <c r="Q39">
+        <v>115</v>
+      </c>
       <c r="R39" t="b">
         <v>0</v>
       </c>
@@ -2646,7 +2682,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>21</v>
       </c>
@@ -2676,6 +2712,9 @@
       </c>
       <c r="P40" t="s">
         <v>76</v>
+      </c>
+      <c r="Q40">
+        <v>115</v>
       </c>
       <c r="R40" t="b">
         <v>0</v>
